--- a/hpi_scraper/Firmographic/apollo/apollo_data.xlsx
+++ b/hpi_scraper/Firmographic/apollo/apollo_data.xlsx
@@ -445,16 +445,16 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="9" max="9"/>
+    <col width="53" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
@@ -536,65 +536,53 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Singtel</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>singtel.com</t>
-        </is>
-      </c>
+          <t>Secure Electronic Applications Ltd</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>http://www.linkedin.com/company/singtel</t>
+          <t>http://www.linkedin.com/company/sea-ltd</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>4.12%</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>10.5B</t>
-        </is>
-      </c>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>telecommunications</t>
+          <t>electrical/electronic manufacturing</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>telecommunications | information technology &amp; services | computer &amp; network security | computer networking | internet | NAICS: 517111 | 517112 | 541512 | SIC: 4812</t>
+          <t>electrical/electronic manufacturing</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>10 Eunos Road 8, Singapore Post Centre #07-31, Singapore, 408600, SG</t>
+          <t>36 Pearson Way, Questor, Dartford, Kent DA1 1JN, GB</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>1879</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Public Company</t>
-        </is>
-      </c>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="inlineStr"/>
     </row>
   </sheetData>
